--- a/south.xlsx
+++ b/south.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2f3df39ef44ce0b8/Desktop/Jayanagar/notice dashboard/deepseek/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2f3df39ef44ce0b8/Desktop/Jayanagar/2002/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18DA7400-1CBC-4E1D-8D27-67602E327160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_043449E393EE69DAF08E0719ED4F5CD7F907F839" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D50EBB11-E608-41BE-8B22-450D3CC9C5BE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
